--- a/pregenerated_results/att_iptw_gee_IPTW_GEE_turnover_intention_index_mgr.xlsx
+++ b/pregenerated_results/att_iptw_gee_IPTW_GEE_turnover_intention_index_mgr.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.024</v>
+        <v>-0.066</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.002</v>
+        <v>0.007</v>
       </c>
       <c r="E7" t="n">
-        <v>0.022</v>
+        <v>0.059</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.046</v>
+        <v>0.227</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="E8" t="n">
-        <v>0.045</v>
+        <v>0.225</v>
       </c>
       <c r="F8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.392</v>
       </c>
       <c r="D9" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="F9" t="b">
         <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="F9" t="b">
-        <v>1</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,16 +696,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.074</v>
+        <v>-0.401</v>
       </c>
       <c r="D10" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="E10" t="n">
-        <v>0.06999999999999999</v>
+        <v>0.396</v>
       </c>
       <c r="F10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.034</v>
+        <v>-0.054</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001</v>
+        <v>0.006</v>
       </c>
       <c r="E11" t="n">
-        <v>0.033</v>
+        <v>0.048</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.023</v>
+        <v>0.077</v>
       </c>
       <c r="D12" t="n">
-        <v>0.004</v>
+        <v>-0.002</v>
       </c>
       <c r="E12" t="n">
-        <v>0.019</v>
+        <v>0.075</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="E13" t="n">
         <v>0.007</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.006</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,13 +804,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.041</v>
+        <v>0.007</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.001</v>
       </c>
       <c r="E14" t="n">
-        <v>0.032</v>
+        <v>0.006</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.005</v>
+        <v>0.032</v>
       </c>
       <c r="D15" t="n">
-        <v>0.007</v>
+        <v>-0.005</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.002</v>
+        <v>0.027</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.032</v>
+        <v>0.022</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.004</v>
+        <v>-0.003</v>
       </c>
       <c r="E16" t="n">
-        <v>0.028</v>
+        <v>0.019</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.014</v>
+        <v>0.005</v>
       </c>
       <c r="D17" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="E17" t="n">
-        <v>0.012</v>
+        <v>-0.002</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,16 +912,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0</v>
+        <v>0.197</v>
       </c>
       <c r="D18" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="F18" t="b">
         <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="b">
-        <v>1</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.008</v>
+        <v>-0.143</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.002</v>
+        <v>0.003</v>
       </c>
       <c r="E19" t="n">
-        <v>0.006</v>
+        <v>0.14</v>
       </c>
       <c r="F19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.077</v>
+        <v>0.034</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.001</v>
+        <v>0.001</v>
       </c>
       <c r="E20" t="n">
-        <v>0.076</v>
+        <v>0.033</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.019</v>
+        <v>-0</v>
       </c>
       <c r="D21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.113</v>
+        <v>-0.019</v>
       </c>
       <c r="D22" t="n">
-        <v>0.003</v>
+        <v>-0</v>
       </c>
       <c r="E22" t="n">
-        <v>0.11</v>
+        <v>0.019</v>
       </c>
       <c r="F22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.197</v>
+        <v>-0.128</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.006</v>
+        <v>-0.003</v>
       </c>
       <c r="E23" t="n">
-        <v>0.191</v>
+        <v>0.125</v>
       </c>
       <c r="F23" t="b">
         <v>0</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,16 +1074,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.143</v>
+        <v>-0.074</v>
       </c>
       <c r="D24" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="E24" t="n">
-        <v>0.14</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="F24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,16 +1101,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.054</v>
+        <v>0.107</v>
       </c>
       <c r="D25" t="n">
-        <v>0.006</v>
+        <v>-0.003</v>
       </c>
       <c r="E25" t="n">
-        <v>0.048</v>
+        <v>0.104</v>
       </c>
       <c r="F25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,16 +1128,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-0.128</v>
+        <v>-0.014</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.002</v>
+        <v>0.002</v>
       </c>
       <c r="E26" t="n">
-        <v>0.126</v>
+        <v>0.012</v>
       </c>
       <c r="F26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,16 +1155,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.227</v>
+        <v>0.046</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="E27" t="n">
-        <v>0.225</v>
+        <v>0.045</v>
       </c>
       <c r="F27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,16 +1182,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.392</v>
+        <v>-0.041</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.008</v>
+        <v>-0</v>
       </c>
       <c r="E28" t="n">
-        <v>0.384</v>
+        <v>0.041</v>
       </c>
       <c r="F28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,16 +1209,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.401</v>
+        <v>0.041</v>
       </c>
       <c r="D29" t="n">
-        <v>0.005</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>0.396</v>
+        <v>0.032</v>
       </c>
       <c r="F29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,16 +1236,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.107</v>
+        <v>-0.024</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.003</v>
+        <v>-0.001</v>
       </c>
       <c r="E30" t="n">
-        <v>0.104</v>
+        <v>0.023</v>
       </c>
       <c r="F30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.041</v>
+        <v>0.023</v>
       </c>
       <c r="D31" t="n">
-        <v>-0</v>
+        <v>0.004</v>
       </c>
       <c r="E31" t="n">
-        <v>0.041</v>
+        <v>0.019</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.066</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0.059</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1308,7 +1308,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1317,18 +1317,45 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.022</v>
+        <v>-0.113</v>
       </c>
       <c r="D33" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>baseline_turnover_intention</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="D34" t="n">
         <v>-0.004</v>
       </c>
-      <c r="E33" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="F33" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" t="b">
+      <c r="E34" t="n">
+        <v>0.03700000000000001</v>
+      </c>
+      <c r="F34" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1388,13 +1415,13 @@
         <v>7220</v>
       </c>
       <c r="B2" t="n">
-        <v>554.8319074166568</v>
+        <v>554.8400919266784</v>
       </c>
       <c r="C2" t="n">
-        <v>0.07201588164977409</v>
+        <v>0.07201645070699485</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2496221955703657</v>
+        <v>0.2496221736559741</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -1464,19 +1491,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.415563718989385</v>
+        <v>1.416217032035464</v>
       </c>
       <c r="C2" t="n">
-        <v>0.365379294542185</v>
+        <v>0.3656412703783339</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6994334609900499</v>
+        <v>0.6995733108324573</v>
       </c>
       <c r="E2" t="n">
-        <v>2.13169397698872</v>
+        <v>2.132860753238471</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0001069620034727728</v>
+        <v>0.0001073972031422921</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,19 +1516,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01406648442462925</v>
+        <v>0.0142281241730207</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06948450970190397</v>
+        <v>0.06947680535512635</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1221206520745265</v>
+        <v>-0.1219439120839265</v>
       </c>
       <c r="E3" t="n">
-        <v>0.150253620923785</v>
+        <v>0.1504001604299679</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8395723070577614</v>
+        <v>0.8377365466044563</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,19 +1541,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1934376197861498</v>
+        <v>0.1933812898596145</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1561342593458452</v>
+        <v>0.1561332088472189</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1125799052845433</v>
+        <v>-0.1126341762716051</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4994551448568428</v>
+        <v>0.499396755990834</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2153756879251695</v>
+        <v>0.2155062519099162</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1539,19 +1566,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08228016691387016</v>
+        <v>0.08233050997766937</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1200746414081911</v>
+        <v>0.1200862923990153</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1530618057027462</v>
+        <v>-0.1530342981613467</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3176221395304866</v>
+        <v>0.3176953181166854</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4931913324621544</v>
+        <v>0.492968806741948</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1591,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2682770111457028</v>
+        <v>0.2683078778921119</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1300132400848991</v>
+        <v>0.1300161595012189</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01345574306594133</v>
+        <v>0.0134808878615077</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5230982792254644</v>
+        <v>0.5231348679227161</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03906902418388717</v>
+        <v>0.03905089109964354</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1616,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05866897476675006</v>
+        <v>0.05880343035382379</v>
       </c>
       <c r="C7" t="n">
-        <v>0.138655478374334</v>
+        <v>0.1386733211694758</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2130907691061169</v>
+        <v>-0.2129912847549045</v>
       </c>
       <c r="E7" t="n">
-        <v>0.330428718639617</v>
+        <v>0.3305981454625521</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6722020875369367</v>
+        <v>0.6715345632193579</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1641,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.06280541537249594</v>
+        <v>0.06291103265427977</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1473120129983399</v>
+        <v>0.147323013727779</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2259208245943466</v>
+        <v>-0.2258367683460671</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3515316553393385</v>
+        <v>0.3516588336546266</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6698580785094375</v>
+        <v>0.6693590288339228</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1639,19 +1666,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1390231384900846</v>
+        <v>0.1390734913241863</v>
       </c>
       <c r="C9" t="n">
-        <v>0.120288228326492</v>
+        <v>0.1203010301804612</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.09673745679397053</v>
+        <v>-0.09671219513258381</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3747837337741398</v>
+        <v>0.3748591777809565</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2477833667498961</v>
+        <v>0.2476624555639129</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,19 +1691,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02793986317350415</v>
+        <v>0.02815120951285042</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1999310656891016</v>
+        <v>0.1999368381277357</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3639178249678467</v>
+        <v>-0.3637177924003261</v>
       </c>
       <c r="E10" t="n">
-        <v>0.419797551314855</v>
+        <v>0.420020211426027</v>
       </c>
       <c r="F10" t="n">
-        <v>0.888859508592426</v>
+        <v>0.8880275372472282</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,19 +1716,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.07356614672567961</v>
+        <v>-0.07320072022610642</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2061356399317545</v>
+        <v>0.2061355728393927</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.477584576922035</v>
+        <v>-0.4772190189238492</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3304522834706757</v>
+        <v>0.3308175784716363</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7211799737560176</v>
+        <v>0.7225074871352848</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1741,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.03199774539716469</v>
+        <v>0.03214819100179273</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2061594449032442</v>
+        <v>0.2061683792653424</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3720673416859635</v>
+        <v>-0.3719344071092728</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4360628324802929</v>
+        <v>0.4362307891128583</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8766567670029295</v>
+        <v>0.8760868383009752</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1766,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.006374277414136828</v>
+        <v>-0.00632140260804195</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1965463686430544</v>
+        <v>0.1965468484203017</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.391598081246656</v>
+        <v>-0.3915461467866865</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3788495264183824</v>
+        <v>0.3789033415706027</v>
       </c>
       <c r="F13" t="n">
-        <v>0.974128007815297</v>
+        <v>0.9743426050118166</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1791,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.2378369521738856</v>
+        <v>-0.237831773985135</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2077401681853177</v>
+        <v>0.2077477918600027</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.6450001999594019</v>
+        <v>-0.6450099638984637</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1693262956116307</v>
+        <v>0.1693464159281937</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2522600895661893</v>
+        <v>0.252287823367096</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1816,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.08511172439276508</v>
+        <v>-0.08500413340390582</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2148668528732521</v>
+        <v>0.2148717116446603</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.5062430174958057</v>
+        <v>-0.5061449495239158</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3360195687102756</v>
+        <v>0.3361366827161041</v>
       </c>
       <c r="F15" t="n">
-        <v>0.692021082380699</v>
+        <v>0.6923971006553898</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1841,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.09645326976338127</v>
+        <v>0.09659014025845707</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1999648883531895</v>
+        <v>0.19997206191965</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2954707095814431</v>
+        <v>-0.2953478990182705</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4883772491082056</v>
+        <v>0.4885281795351847</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6295566025541425</v>
+        <v>0.6290828318257051</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1866,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.2658960001519032</v>
+        <v>-0.2660395190054231</v>
       </c>
       <c r="C17" t="n">
-        <v>0.197363342096245</v>
+        <v>0.1973461079556876</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6527210425290013</v>
+        <v>-0.6528307830877242</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1209290422251949</v>
+        <v>0.1207517450768781</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1779026046618565</v>
+        <v>0.177630733989855</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1891,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.1410581106617718</v>
+        <v>0.1413128269387598</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1862982201656767</v>
+        <v>0.1862951698661591</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2240796912468682</v>
+        <v>-0.2238189964926836</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5061959125704119</v>
+        <v>0.5064446503702031</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4489522418144468</v>
+        <v>0.4481262062872127</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1916,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.08344985283767346</v>
+        <v>-0.0834525454682276</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2041354907480704</v>
+        <v>0.2041393115207918</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4835480626703009</v>
+        <v>-0.483558243877782</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3166483569949539</v>
+        <v>0.3166531529413268</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6826890852425073</v>
+        <v>0.6826850200918814</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1941,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.2678101521998024</v>
+        <v>-0.2677188095404624</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1911082668602463</v>
+        <v>0.1911182059576983</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6423754723937547</v>
+        <v>-0.6423036100074595</v>
       </c>
       <c r="E20" t="n">
-        <v>0.10675516799415</v>
+        <v>0.1068659909265346</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1611085253078218</v>
+        <v>0.161273220927346</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1966,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.2357850011436261</v>
+        <v>-0.235699031137386</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1852596407770945</v>
+        <v>0.1852489778184468</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5988872248555595</v>
+        <v>-0.5987803558344011</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1273172225683072</v>
+        <v>0.1273822935596291</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2031148290792987</v>
+        <v>0.2032535947278427</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1991,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.05887556586940924</v>
+        <v>0.05890136737479215</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1964795852898691</v>
+        <v>0.196483719440351</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3262173449961</v>
+        <v>-0.3261996462767683</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4439684767349185</v>
+        <v>0.4440023810263527</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7644423623312745</v>
+        <v>0.7643469985561084</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +2016,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.137097838596114</v>
+        <v>-0.1369387830363407</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2015940271276349</v>
+        <v>0.2016102966569472</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.532214871264669</v>
+        <v>-0.5320877033963932</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2580191940724411</v>
+        <v>0.2582101373237119</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4964608030112675</v>
+        <v>0.4969952171557461</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2041,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1314300700432246</v>
+        <v>0.1312809288888285</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1025093436987393</v>
+        <v>0.1025088920042636</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.06948455168514242</v>
+        <v>-0.06963280753463405</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3323446917715916</v>
+        <v>0.3321946653122911</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1997978500285615</v>
+        <v>0.2003066322422055</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2066,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.03463267714177366</v>
+        <v>0.03459976437175145</v>
       </c>
       <c r="C25" t="n">
-        <v>0.08275182901981308</v>
+        <v>0.08275643967438231</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1275579273918764</v>
+        <v>-0.1275998768787995</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1968232816754238</v>
+        <v>0.1967994056223024</v>
       </c>
       <c r="F25" t="n">
-        <v>0.67557242895257</v>
+        <v>0.6758802160970294</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2091,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1488260434975335</v>
+        <v>-0.1487391136497862</v>
       </c>
       <c r="C26" t="n">
-        <v>0.104119204422446</v>
+        <v>0.1041170930993672</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3528959342644912</v>
+        <v>-0.3528048662995497</v>
       </c>
       <c r="E26" t="n">
-        <v>0.05524384726942427</v>
+        <v>0.05532663899997736</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1528946709271366</v>
+        <v>0.1531263206557859</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2116,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.03169527812066093</v>
+        <v>-0.03162286056299789</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1100545842581243</v>
+        <v>0.1100527203296481</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2473982996001133</v>
+        <v>-0.2473222288097672</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1840077433587915</v>
+        <v>0.1840765076837714</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7733498139601125</v>
+        <v>0.7738498279546902</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2141,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1415579970155403</v>
+        <v>0.1414988001844074</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1155062953631742</v>
+        <v>0.1154973281423105</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.0848301818839271</v>
+        <v>-0.08487180328512572</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3679461759150076</v>
+        <v>0.3678694036539404</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2203704862681708</v>
+        <v>0.2205276833485572</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2166,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.02793447775400486</v>
+        <v>-0.02801905536226728</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1096742534746417</v>
+        <v>0.1096652170544505</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.2428920645956195</v>
+        <v>-0.242958931145758</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1870231090876098</v>
+        <v>0.1869208204212234</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7989516794020008</v>
+        <v>0.7983398138934068</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,19 +2191,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2582177129441012</v>
+        <v>0.2575394572180181</v>
       </c>
       <c r="C30" t="n">
-        <v>0.03790343166340591</v>
+        <v>0.0377013629120963</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1839283519933505</v>
+        <v>0.1836461437422353</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3325070738948519</v>
+        <v>0.331432770693801</v>
       </c>
       <c r="F30" t="n">
-        <v>9.590676754544794e-12</v>
+        <v>8.430217045679813e-12</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2185,23 +2212,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.06813476221211853</v>
+        <v>0.001079405240890579</v>
       </c>
       <c r="C31" t="n">
-        <v>0.07489655592157836</v>
+        <v>0.005977528859952302</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.07865978996026518</v>
+        <v>-0.0106363360411647</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2149293143845022</v>
+        <v>0.01279514652294586</v>
       </c>
       <c r="F31" t="n">
-        <v>0.36297112811455</v>
+        <v>0.8566994775233749</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2210,23 +2237,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.001079790152347911</v>
+        <v>-0.01398407748847818</v>
       </c>
       <c r="C32" t="n">
-        <v>0.005978338076640147</v>
+        <v>0.01558973257530604</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.01063753716527123</v>
+        <v>-0.04453939186468887</v>
       </c>
       <c r="E32" t="n">
-        <v>0.01279711746996706</v>
+        <v>0.01657123688773252</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8566681240955263</v>
+        <v>0.3697159265772327</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2235,23 +2262,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.004135564358761948</v>
+        <v>0.001907819015519182</v>
       </c>
       <c r="C33" t="n">
-        <v>0.004941189696127534</v>
+        <v>0.004864235898725821</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.005548989486428432</v>
+        <v>-0.007625908158290249</v>
       </c>
       <c r="E33" t="n">
-        <v>0.01382011820395233</v>
+        <v>0.01144154618932861</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4026166188305283</v>
+        <v>0.6949004657097185</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2260,23 +2287,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.01398274283089321</v>
+        <v>0.004132983949690939</v>
       </c>
       <c r="C34" t="n">
-        <v>0.01558971665227964</v>
+        <v>0.00494123768072603</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.04453802599854564</v>
+        <v>-0.005551663943584307</v>
       </c>
       <c r="E34" t="n">
-        <v>0.01657254033675923</v>
+        <v>0.01381763184296619</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3697611220226229</v>
+        <v>0.4029148035609804</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,23 +2312,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>baseline_turnover_intention</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.00191588801380837</v>
+        <v>0.4698832587018675</v>
       </c>
       <c r="C35" t="n">
-        <v>0.004864009007753421</v>
+        <v>0.03331028861871325</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.007617394461866739</v>
+        <v>0.404596292694555</v>
       </c>
       <c r="E35" t="n">
-        <v>0.01144917048948348</v>
+        <v>0.53517022470918</v>
       </c>
       <c r="F35" t="n">
-        <v>0.6936617214919621</v>
+        <v>3.475754395965104e-45</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2310,23 +2337,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>baseline_turnover_intention</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.4698373208221375</v>
+        <v>0.06785251178112445</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0333286157828773</v>
+        <v>0.07489053896432142</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4045144342331247</v>
+        <v>-0.07893024737173915</v>
       </c>
       <c r="E36" t="n">
-        <v>0.5351602074111502</v>
+        <v>0.214635270933988</v>
       </c>
       <c r="F36" t="n">
-        <v>3.956166429173207e-45</v>
+        <v>0.3649239544330217</v>
       </c>
       <c r="G36" t="n">
         <v>0.05</v>
@@ -2343,7 +2370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2375,13 +2402,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.680600179802939</v>
+        <v>-2.820303044554362</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4771933030981503</v>
+        <v>0.5099234395092979</v>
       </c>
       <c r="D2" t="n">
-        <v>1.938181768273511e-08</v>
+        <v>3.187077352409629e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2391,13 +2418,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.02542074333516161</v>
+        <v>-0.02464939576457233</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1002143663033998</v>
+        <v>0.1003099681595394</v>
       </c>
       <c r="D3" t="n">
-        <v>0.79975540801217</v>
+        <v>0.8058894933269584</v>
       </c>
     </row>
     <row r="4">
@@ -2407,13 +2434,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2244463748843409</v>
+        <v>0.2249663577428585</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2335027157442915</v>
+        <v>0.2337176582603367</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3364439424069162</v>
+        <v>0.3357703370011805</v>
       </c>
     </row>
     <row r="5">
@@ -2423,13 +2450,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8155080917228588</v>
+        <v>0.8191373674885462</v>
       </c>
       <c r="C5" t="n">
-        <v>0.173402651392118</v>
+        <v>0.1734167828528219</v>
       </c>
       <c r="D5" t="n">
-        <v>2.563995828054386e-06</v>
+        <v>2.317989576597557e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2439,13 +2466,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03527526670387308</v>
+        <v>0.03652125765996361</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1916882946919544</v>
+        <v>0.1917132959179625</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8539945454713548</v>
+        <v>0.8489178549322628</v>
       </c>
     </row>
     <row r="7">
@@ -2455,13 +2482,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2773648159307716</v>
+        <v>0.2789564326928404</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1901447102133385</v>
+        <v>0.190113990622697</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1446466431125523</v>
+        <v>0.1422913540098498</v>
       </c>
     </row>
     <row r="8">
@@ -2471,13 +2498,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1036811851537241</v>
+        <v>0.1068531552827687</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1952515666982444</v>
+        <v>0.1953287956048307</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5954095400432469</v>
+        <v>0.5843495250374464</v>
       </c>
     </row>
     <row r="9">
@@ -2487,13 +2514,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8738774480300985</v>
+        <v>0.8765772051307453</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1695280942409139</v>
+        <v>0.1697332036095897</v>
       </c>
       <c r="D9" t="n">
-        <v>2.539495077342821e-07</v>
+        <v>2.411578475116454e-07</v>
       </c>
     </row>
     <row r="10">
@@ -2503,13 +2530,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.0445652077261707</v>
+        <v>-0.0444798686603073</v>
       </c>
       <c r="C10" t="n">
-        <v>0.260402103171632</v>
+        <v>0.2604513322559263</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8641137091517843</v>
+        <v>0.864396785492989</v>
       </c>
     </row>
     <row r="11">
@@ -2519,13 +2546,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.2737623724798146</v>
+        <v>-0.2727472209256586</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2787881385465067</v>
+        <v>0.2791278961561447</v>
       </c>
       <c r="D11" t="n">
-        <v>0.326113242387764</v>
+        <v>0.3284995130487423</v>
       </c>
     </row>
     <row r="12">
@@ -2535,13 +2562,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08100487957118148</v>
+        <v>0.07889678868393071</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2596429772097172</v>
+        <v>0.2596148796948632</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7550514391424692</v>
+        <v>0.7612045862333787</v>
       </c>
     </row>
     <row r="13">
@@ -2551,13 +2578,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03917827337461754</v>
+        <v>0.04019393041481616</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2572958805743774</v>
+        <v>0.2574204041328308</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8789745077123743</v>
+        <v>0.8759217249007</v>
       </c>
     </row>
     <row r="14">
@@ -2567,13 +2594,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.05296103812307935</v>
+        <v>-0.04910228165084287</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2610089865588724</v>
+        <v>0.2612561015991025</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8392062624375534</v>
+        <v>0.8509182551619311</v>
       </c>
     </row>
     <row r="15">
@@ -2583,13 +2610,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1181322726534161</v>
+        <v>0.1160743543422989</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2572294350577187</v>
+        <v>0.2571236264961854</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6460556128984086</v>
+        <v>0.6516767631413001</v>
       </c>
     </row>
     <row r="16">
@@ -2599,13 +2626,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.004000986240379481</v>
+        <v>-0.002512421030226088</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2383903410311192</v>
+        <v>0.2386078717504883</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9866094604655132</v>
+        <v>0.9915988316144653</v>
       </c>
     </row>
     <row r="17">
@@ -2615,13 +2642,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1057185310395306</v>
+        <v>0.1088094847883374</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2543340222421759</v>
+        <v>0.2546184298925984</v>
       </c>
       <c r="D17" t="n">
-        <v>0.677652912256731</v>
+        <v>0.6691292855457329</v>
       </c>
     </row>
     <row r="18">
@@ -2631,13 +2658,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1377694895733254</v>
+        <v>-0.1371054629493665</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2636874203313636</v>
+        <v>0.26372382153466</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6013412201546282</v>
+        <v>0.6031453060319996</v>
       </c>
     </row>
     <row r="19">
@@ -2647,13 +2674,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02557154094223237</v>
+        <v>-0.02469784288290774</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2527597901538116</v>
+        <v>0.252905825477516</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9194160355966677</v>
+        <v>0.9222052306173931</v>
       </c>
     </row>
     <row r="20">
@@ -2663,13 +2690,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.07344622569376411</v>
+        <v>-0.06845683158478749</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2674578609541021</v>
+        <v>0.267301158451401</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7836169672222787</v>
+        <v>0.7978707191500396</v>
       </c>
     </row>
     <row r="21">
@@ -2679,13 +2706,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2063167170305062</v>
+        <v>0.2086621675742921</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2442896532450728</v>
+        <v>0.2442815662419185</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3983578134719854</v>
+        <v>0.3930013184626183</v>
       </c>
     </row>
     <row r="22">
@@ -2695,13 +2722,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1704634573362028</v>
+        <v>-0.175406708188101</v>
       </c>
       <c r="C22" t="n">
-        <v>0.269674845496591</v>
+        <v>0.2700541998112392</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5273167196806365</v>
+        <v>0.51599968117048</v>
       </c>
     </row>
     <row r="23">
@@ -2711,13 +2738,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.5008110927334755</v>
+        <v>-0.5004384224930736</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2870672180445716</v>
+        <v>0.2870894861894652</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0810583897517186</v>
+        <v>0.08130839926920327</v>
       </c>
     </row>
     <row r="24">
@@ -2727,13 +2754,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9366864721074268</v>
+        <v>0.9379041483579631</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1483430409733375</v>
+        <v>0.1484949273354127</v>
       </c>
       <c r="D24" t="n">
-        <v>2.713396260923871e-10</v>
+        <v>2.683009814405772e-10</v>
       </c>
     </row>
     <row r="25">
@@ -2743,13 +2770,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5776106069409677</v>
+        <v>-0.5776000776467408</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1143619392421806</v>
+        <v>0.1143336799033598</v>
       </c>
       <c r="D25" t="n">
-        <v>4.401383208103854e-07</v>
+        <v>4.374815955439373e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2759,13 +2786,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2373161448441742</v>
+        <v>0.2357452695510328</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1503781926377481</v>
+        <v>0.1505208025229895</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1145360411757815</v>
+        <v>0.1173024423291913</v>
       </c>
     </row>
     <row r="27">
@@ -2775,13 +2802,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.04350476117998643</v>
+        <v>-0.04479861183336151</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1611879340386415</v>
+        <v>0.161178325869642</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7872365295400221</v>
+        <v>0.7810550458340707</v>
       </c>
     </row>
     <row r="28">
@@ -2791,13 +2818,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.07514354096975739</v>
+        <v>-0.07528727625378248</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1613683918223571</v>
+        <v>0.1614983128820299</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6414556246120158</v>
+        <v>0.6410866959853156</v>
       </c>
     </row>
     <row r="29">
@@ -2807,93 +2834,109 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09749293462742094</v>
+        <v>0.09387617646092147</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1543265796290169</v>
+        <v>0.1543340718197336</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5275624553510021</v>
+        <v>0.5430110331238939</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2280638724458788</v>
+        <v>-0.004826402612991651</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1146565719927948</v>
+        <v>0.008314480096143072</v>
       </c>
       <c r="D30" t="n">
-        <v>0.04668969945129902</v>
+        <v>0.5615898992578201</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.005012017390962181</v>
+        <v>-0.003793322855986116</v>
       </c>
       <c r="C31" t="n">
-        <v>0.008304876992454899</v>
+        <v>0.02223202690000074</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5461741835341518</v>
+        <v>0.8645192309060573</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.002418133412192865</v>
+        <v>0.006311908087997972</v>
       </c>
       <c r="C32" t="n">
-        <v>0.007135781003458533</v>
+        <v>0.006867343796543279</v>
       </c>
       <c r="D32" t="n">
-        <v>0.7347043603418282</v>
+        <v>0.3580331856516411</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.004129656026475429</v>
+        <v>-0.002469929930368323</v>
       </c>
       <c r="C33" t="n">
-        <v>0.02222260881033176</v>
+        <v>0.007130763690581499</v>
       </c>
       <c r="D33" t="n">
-        <v>0.8525770672961277</v>
+        <v>0.7290596823423179</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>baseline_turnover_intention</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.006335499136474494</v>
+        <v>0.04715208655231711</v>
       </c>
       <c r="C34" t="n">
-        <v>0.006871422968197173</v>
+        <v>0.04889616403699384</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3565249957666431</v>
+        <v>0.3348800057442061</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>is_new_manager</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.225647909614498</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.1147189874002693</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.04918757099961349</v>
       </c>
     </row>
   </sheetData>
